--- a/거시경제_상황_레포트_2026-07.xlsx
+++ b/거시경제_상황_레포트_2026-07.xlsx
@@ -11,7 +11,8 @@
     <sheet name="미시경제" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="거시경제" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="국제경제" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="출처(Sources)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="국내기관전망" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="출처(Sources)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -559,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -625,7 +626,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>3개 시트 — ①미시경제 ②거시경제 ③국제경제</t>
+          <t>①미시경제 ②거시경제 ③국제경제 ④국내기관전망 (+요약·출처)</t>
         </is>
       </c>
       <c r="C7" s="5" t="n"/>
@@ -648,236 +649,251 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>주요 출처</t>
+          <t>참고 레포트</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>美 연준·BLS, 한국은행·KDI, IMF·EIA·세계은행, Eurostat, 中 NBS</t>
+          <t>국내 15개+ 기관 취합: 기재부·한은·KDI·KIET·KIEP·KIF·KCIF·KITA·HRI·삼일PwC·삼정KPMG·NABO 등</t>
         </is>
       </c>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="6" t="n"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>해외 출처</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>美 연준·BLS, IMF·EIA·세계은행, Eurostat, 中 NBS</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="6" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>■ 한눈에 보는 핵심 지표 (2026년 6월 기준)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>지표</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>한국</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>미국</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>정책(기준)금리</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>2.50%</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>3.50~3.75%</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>美 6/17 동결·매파적</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>소비자물가(YoY)</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>2.6% (4월)</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>4.2% (5월, CPI)</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>유가발 상방 압력</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>성장률 전망('26)</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>2.6%</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>2.2%</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>한은/연준 전망</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>실업률</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>약 2.8%</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>4.2% (6월)</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>美 고용 둔화</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>환율·달러</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>USD/KRW ≈1,554</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>DXY ≈100.7</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>원화 약세·달러 강세</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>증시(YTD)</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>코스피 변동성 확대</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>S&amp;P500 +9.6%</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>AI랠리·전쟁 변수</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>■ 현 국면 3줄 요약</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>1) 中東(중동) 분쟁·호르무즈 해협 봉쇄 장기화로 국제유가가 급등하며 글로벌 인플레이션이 재점화됨.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2) 美 연준은 금리를 동결했으나 물가 상방으로 매파적 선회(연내 인상 가능성), 달러 강세·원화 약세가 심화.</t>
+          <t>1) 中東(중동) 분쟁·호르무즈 해협 봉쇄 장기화로 국제유가가 급등하며 글로벌 인플레이션이 재점화됨.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
+          <t>2) 美 연준은 금리를 동결했으나 물가 상방으로 매파적 선회(연내 인상 가능성), 달러 강세·원화 약세가 심화.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
           <t>3) 한국은 반도체 수출 호조로 성장 전망은 상향됐으나, 고환율·가계부채·부동산 PF가 하방 리스크로 상존.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>※ 본 자료는 공개된 통계·전망을 요약한 참고용이며, 투자판단의 근거로 사용될 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
+          <t>※ 본 자료는 공개된 통계·전망을 요약한 참고용이며, 투자판단의 근거로 사용될 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
           <t>※ 일부 수치는 잠정치/기관 전망치로, 발표기관·시점에 따라 달라질 수 있습니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
+    <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="B8:D8"/>
-    <mergeCell ref="A20:D20"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A24:D24"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B7:D7"/>
+    <mergeCell ref="A28:D28"/>
     <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -890,13 +906,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="4" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1527,29 +1543,353 @@
       </c>
       <c r="E33" s="9" t="inlineStr"/>
     </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>■ 가계부채·부동산 (Household Debt &amp; Real Estate) — 국내기관 취합</t>
+        </is>
+      </c>
+    </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>값/내용</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>시점</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>GDP 대비 가계부채</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>89.3%</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>'25 3분기</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>우리금융/한은</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>'21 98.7%→하향 안정화</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>가계부채 국제비교</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>주요국 中 5위 수준</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>우리금융경영연구소</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>여전히 높은 편</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>가계부채 관리방안</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>관리 강화 기조 지속</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>2026.04.01</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>금융위원회</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>생산적 분야로 자금 유도</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>다주택 규제</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>수도권 규제지역 주담대 만기연장 원칙 불허</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>2026.04.17~</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>금융위</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>다주택 양도세 중과 유예 종료(5/9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>부동산 PF</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>건전성 리스크 상존</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>KDI/현대硏</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>내수·금융 하방 요인</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>■ 반도체 부문 심층 (Semiconductor Deep-Dive) — KITA/KIET</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>값/내용</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>'25 반도체 수출</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>사상 최고 ≈1,419억달러 경신 전망</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>무역협회(KITA)</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>하반기 30% 내외 증가</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>글로벌 반도체 시장('26)</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>+17.8% → 9,098억달러</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>무역협회(KITA)</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>AI 투자 확대</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>수급 구조</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>범용 DRAM 공급부족 + AI 수요 급증</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>KITA</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>고부가 중심 재편</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>'26 주력산업(호조)</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>반도체·ICT·조선·바이오헬스</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>산업연구원(KIET)</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>견고한 성장</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>'26 부진산업</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>철강·석유화학·정유(침체), 車·섬유(정체)</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>산업연구원(KIET)</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>양극화 심화</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t>※ 미시 지표는 가계·기업·부문 등 개별 경제주체 수준의 흐름을 보여줍니다.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
         <is>
           <t>※ 美 고용 = BLS 2026년 6월 고용상황 보고서. 韓 지표 = 한국은행·언론 취합(일부 잠정).</t>
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>※ 가계부채·반도체 = 우리금융경영연구소·금융위·한국무역협회·산업연구원 자료 취합.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="11">
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A36:E36"/>
     <mergeCell ref="A22:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1562,14 +1902,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -2084,32 +2424,326 @@
         </is>
       </c>
     </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>■ 국내기관 '26 한국 성장률 전망 컨센서스</t>
+        </is>
+      </c>
+    </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>기관</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>성장률('26)</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>물가</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>발표/기준</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>기획재정부</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>2.0% (목표)</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>경제성장전략</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>잠재성장률 반등 목표</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>한국은행</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>1.8% → 상향(2.6%)</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>'26 상반기</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>반도체 수출 반영 상향</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>KDI</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>2.5% ('27 1.7%)</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>2026.05.13</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>반도체+내수 개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>산업연구원(KIET)</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>'26 전망</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>AI·반도체 강세</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>한국금융연구원(KIF)</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>'26 전망</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>금융완화·정책효과</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>삼일PwC</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>2% 내외</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>'26 전망</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>저성장 지속</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>현대경제연구원(HRI)</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>'25.9 기준</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>실업률 3.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>국회예산정책처(NABO)</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>'26 전망</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>IMF(참고)</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>'26</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>회복 국면 진입 평가</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>※ 전망 편차(1.8~2.6%)는 발표시점 차이 때문: 2025년말~'26초 전망은 관세·수출둔화 우려로 보수적,</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   '26년 상반기 갱신치(KDI·한은)는 반도체 수출 호조를 반영해 상향된 경향.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>※ 거시 지표는 한 경제 전체의 총량 흐름(성장·물가·고용·금리)을 나타냅니다.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>※ 전망치는 각 중앙은행(한국은행·美 연준)의 공식 전망(2026년 상반기 기준).</t>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>※ 전망치는 각 중앙은행(한국은행·美 연준) 및 국내 주요 연구기관 공식 전망.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="14">
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A46:F46"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2122,14 +2756,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -2661,33 +3295,233 @@
         </is>
       </c>
     </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>■ 국내기관의 세계경제 진단 (KIEP·KCIF·KITA)</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>값/내용</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>세계 성장('26)</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>3.0% (2025년과 동일)</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>대외경제정책연구원(KIEP)</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>'완충된 둔화, 비대칭의 시대'</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>美/유럽/日 성장</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>1.6% / 1.1% / 0.6%</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>KIEP</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>선진국 저성장</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>글로벌 성장(IB)</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>3.1%→2.9%</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>국제금융센터(KCIF)</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>완만한 둔화</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>원/달러 방향</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>달러약세에도 원화강세 제한</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>KCIF</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>수출둔화·대외 불확실성</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>유가('26말 WTI)</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>$90~100 응답 최다</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>KCIF 전문가서베이</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>美·이란 전쟁 여파</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>韓 수출입('26)</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>수출 -0.5% / 무역흑자 675억달러</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>한국무역협회(KITA)</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>기저효과+교역둔화</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>3대 글로벌 리스크</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>중동 에너지충격·美 통상불확실성·재정/국채불안</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>KCIF/KIEP</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>성장 하방 요인</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>※ 국제 지표는 세계 성장·원자재·외환 등 대외 환경을 보여줍니다.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>※ 유가·환율은 변동성이 큰 시점의 스냅샷으로, 실시간 시세와 차이가 있을 수 있습니다.</t>
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>※ 세계경제 진단 = KIEP·국제금융센터(KCIF)·무역협회(KITA) 자료 취합.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A34:E34"/>
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A35:E35"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A33:E33"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A46:E46"/>
     <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A44:E44"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2700,24 +3534,648 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>출처 및 유의사항 (Sources &amp; Notes)</t>
+          <t>④ 국내 주요기관 레포트 종합</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>10개+ 국내 기관 전망 취합 · 2025년말~2026년 상반기 발표</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>■ 기관별 2026년 한국경제 전망 비교</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>기관</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>성장률</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>물가</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>핵심 메시지</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>발표시점</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>기획재정부</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>2.0%(목표)</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>'대한민국 경제大도약 원년', 잠재성장률 반등</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>'26 상반기</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>정부</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>한국은행(BOK)</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>1.8→2.6%</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>반도체 수출 호조로 전망 상향, 금리 2.50% 동결</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>'26 상반기</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>중앙은행</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>KDI</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>반도체+내수 개선, 설비투자 3.3%·소비 2.2%</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>2026.05.13</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>국책</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>산업연구원(KIET)</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>AI·반도체 강세, 산업 양극화</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>'26 전망</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>국책</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>대외경제정책연(KIEP)</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>세계 3.0%, '완충된 둔화·비대칭의 시대'</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>'26 전망</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>국책</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>한국금융연구원(KIF)</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>금융완화·정책효과 반영</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>'26 전망</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>연구원</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>삼일PwC경영연구원</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>2% 내외</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>재정확대 내수가 수출둔화 상쇄, 저성장 지속</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>'25.12</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>민간</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>삼정KPMG경제연구원</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>저성장</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>2026 국내 경제·산업 전망(Business Focus)</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>'25.12</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>민간</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>현대경제연구원(HRI)</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>잠재성장 근접, 회복 미약·실업률 3.0%</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>'25.09</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>민간</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>국회예산정책처(NABO)</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>독립 재정기구 전망</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>'26 전망</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>국회</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>한국무역협회(KITA)</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>수출 -0.5%, 무역흑자 675억달러, 반도체시장 +17.8%</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>'25.12</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>협회</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>국제금융센터(KCIF)</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>글로벌 3.1→2.9%, 원화강세 제한, 유가 리스크</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>'26 전망</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>연구원</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>자본시장연구원(KCMI)</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>2026 거시경제 주요 이슈 분석</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>'26</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>연구원</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>하나금융연구소</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>외환시장 전망(고환율)·대한민국 웰스리포트</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>'26</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>민간</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>우리금융경영연구소</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>가계부채 GDP대비 92%, 주요국 5위 수준</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>'26</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>민간</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>■ 국내기관 공통 진단 (Consensus Themes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>1) 성장: 대체로 잠재성장률(약 2%) 부근. 반도체 사이클을 낙관하는 기관(KDI·KIET 2.5%)과 대외리스크를 무겁게 보는 기관(HRI·NABO 1.9%)으로 갈림.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>2) 물가: 목표(2%) 부근 안정 전망이 다수였으나, 2026년 중동발 유가 급등으로 상방 위험이 재부각(한은 2.7%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>3) 수출: 반도체·AI가 성장의 핵심 엔진. 다만 KITA는 기저효과·교역둔화로 총수출은 소폭 감소(-0.5%) 전망.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>4) 리스크: ①중동 에너지 충격 ②美 관세·통상 불확실성 ③가계부채·부동산 PF ④고환율. 국내기관 공통 3대 대외리스크로 압축.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>5) 정책: 가계부채 관리 강화(금융위), 재정 통한 내수 보강(기재부), 통화정책은 물가·환율에 발목.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>※ 성장률 전망 편차는 발표시점(2025년 하반기 vs 2026년 상반기)과 반도체·대외리스크 가정 차이에서 비롯.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>※ '저성장/목표' 등 수치 미표기 기관은 원문에 단일 수치 대신 서술형 전망을 제시한 경우.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A25:F25"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>출처 및 유의사항 (Sources &amp; Notes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
           <t>2026-07-03 웹 취합</t>
         </is>
       </c>
@@ -2742,41 +4200,41 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>국내(정부)</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>美 연준(FOMC)</t>
+          <t>기획재정부(재정경제부)</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>2026.06.17 FOMC 성명·경제전망(점도표)</t>
+          <t>2026년 경제성장전략</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>국내(정부)</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>美 노동통계국(BLS)</t>
+          <t>금융위원회(FSC)</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>2026년 6월 고용상황 보고서</t>
+          <t>2026년 가계부채 관리방안(2026.04.01)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>국내(중앙은행)</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -2786,111 +4244,315 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>기준금리·물가·성장 전망, 경제통계</t>
+          <t>2026 경제전망보고서, 경제통계·기준금리</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>국내(국책)</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>KDI</t>
+          <t>KDI 한국개발연구원</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>2026 상반기 경제전망</t>
+          <t>KDI 경제전망 2026 상반기(2026.05.13)·경제동향</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>국제</t>
+          <t>국내(국책)</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>IMF</t>
+          <t>산업연구원(KIET)</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>2026년 4월 세계경제전망(WEO)</t>
+          <t>2026년 경제·산업 전망</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>국제</t>
+          <t>국내(국책)</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>EIA / Goldman Sachs / World Bank</t>
+          <t>대외경제정책연구원(KIEP)</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>단기에너지전망(STEO)·원자재 전망</t>
+          <t>2026년 세계경제 전망(업데이트)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>국제</t>
+          <t>국내(국회)</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Eurostat / 中 국가통계국(NBS)</t>
+          <t>국회예산정책처(NABO)</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>유로존·중국 GDP</t>
+          <t>2026 경제전망(성장률 1.9%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
+          <t>국내(연구원)</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>한국금융연구원(KIF)</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>2026년 경제전망과 정책적 시사점</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>국내(연구원)</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>국제금융센터(KCIF)</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>2026 세계경제·국제금융시장 이슈 및 전망</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>국내(연구원)</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>자본시장연구원(KCMI)</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>2026년 거시경제 주요 이슈</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>국내(협회)</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>한국무역협회(KITA)</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>2025 수출입 평가 및 2026 전망·반도체 브리프</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>국내(민간)</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>현대경제연구원(HRI)</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>2026년 한국경제 전망(통권 996호)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>국내(민간)</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>삼일PwC경영연구원</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>2026년 국내외 경제전망</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>국내(민간)</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>삼정KPMG 경제연구원</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>2026년 국내 경제·산업 전망(Business Focus)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>국내(민간)</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>하나금융연구소/하나은행</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>2026 외환시장 전망·대한민국 웰스리포트</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>국내(민간)</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>우리금융경영연구소</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>가계부채 현황·리스크 분석</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>美 연준(FOMC)/BLS</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>2026.06.17 FOMC·6월 고용상황</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>IMF/EIA/World Bank/GS</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>WEO·STEO·원자재 전망</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Eurostat/中 NBS</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>유로존·중국 GDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>CNBC/CNN/Trading Economics 등</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>증시·환율·유가 시세(취합)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>※ 본 레포트는 공개 자료를 요약·재구성한 참고용 문서입니다.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>※ 수치는 발표 시점·기관·개정에 따라 달라질 수 있으며, 정확한 값은 원출처를 확인하십시오.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>※ 작성: 2026-07-03 / 데이터 기준: 2026년 6월(일부 잠정·전망 포함).</t>
         </is>
@@ -2898,11 +4560,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A29:C29"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
